--- a/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.00840949336849749</v>
       </c>
       <c r="C2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>19031370</v>
+        <v>4504376</v>
       </c>
       <c r="L2" t="n">
-        <v>11473760</v>
+        <v>2518880</v>
       </c>
       <c r="M2" t="n">
-        <v>3014158</v>
+        <v>618133</v>
       </c>
       <c r="N2" t="n">
-        <v>191232</v>
+        <v>30117</v>
       </c>
       <c r="O2" t="n">
-        <v>1765485</v>
+        <v>384334</v>
       </c>
       <c r="P2" t="n">
-        <v>691723</v>
+        <v>153648</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999779462814331</v>
+        <v>0.9999785423278809</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9353249073028564</v>
+        <v>0.8796449899673462</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8673853874206543</v>
+        <v>0.7629681825637817</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8327279686927795</v>
+        <v>0.7009280323982239</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6811251044273376</v>
+        <v>0.4526625871658325</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8657050132751465</v>
+        <v>0.7492679357528687</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9067484140396118</v>
+        <v>0.8259313106536865</v>
       </c>
       <c r="X2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="AG2" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AH2" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AI2" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566585421562195</v>
+        <v>0.9564417004585266</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911242663860321</v>
+        <v>0.9113976359367371</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581098318099976</v>
+        <v>0.8579177856445312</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624432802200317</v>
+        <v>0.6617860794067383</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020154476165771</v>
+        <v>0.9019746780395508</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002015272774735009</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>19031370</v>
+        <v>4504376</v>
       </c>
       <c r="E3" t="n">
-        <v>1210307</v>
+        <v>543965</v>
       </c>
       <c r="F3" t="n">
-        <v>20392</v>
+        <v>8049</v>
       </c>
       <c r="G3" t="n">
-        <v>2801</v>
+        <v>1178</v>
       </c>
       <c r="H3" t="n">
-        <v>1020</v>
+        <v>592</v>
       </c>
       <c r="I3" t="n">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="J3" t="n">
-        <v>40277920</v>
+        <v>10069484</v>
       </c>
       <c r="K3" t="n">
-        <v>44081948</v>
+        <v>10741441</v>
       </c>
       <c r="L3" t="n">
-        <v>50800331</v>
+        <v>12348922</v>
       </c>
       <c r="M3" t="n">
-        <v>61323089</v>
+        <v>15217735</v>
       </c>
       <c r="N3" t="n">
-        <v>65217312</v>
+        <v>16290211</v>
       </c>
       <c r="O3" t="n">
-        <v>63352978</v>
+        <v>15777803</v>
       </c>
       <c r="P3" t="n">
-        <v>64819670</v>
+        <v>16190272</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9390747547149658</v>
+        <v>0.8904991149902344</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8752285242080688</v>
+        <v>0.7668906450271606</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8069062829017639</v>
+        <v>0.661444365978241</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5354223847389221</v>
+        <v>0.3369809687137604</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8666462898254395</v>
+        <v>0.7542098164558411</v>
       </c>
       <c r="W3" t="n">
-        <v>0.894632875919342</v>
+        <v>0.7946789860725403</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="Z3" t="n">
-        <v>796241</v>
+        <v>198937</v>
       </c>
       <c r="AA3" t="n">
-        <v>34282</v>
+        <v>8593</v>
       </c>
       <c r="AB3" t="n">
-        <v>27251</v>
+        <v>6842</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40278480</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>44518633</v>
+        <v>11137143</v>
       </c>
       <c r="AG3" t="n">
-        <v>51392586</v>
+        <v>12840927</v>
       </c>
       <c r="AH3" t="n">
-        <v>61398817</v>
+        <v>15348766</v>
       </c>
       <c r="AI3" t="n">
-        <v>65186364</v>
+        <v>16296413</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63427333</v>
+        <v>15856481</v>
       </c>
       <c r="AK3" t="n">
-        <v>64837792</v>
+        <v>16209400</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576596021652222</v>
+        <v>0.9576045870780945</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099968671798706</v>
+        <v>0.9098923206329346</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576393723487854</v>
+        <v>0.8575001358985901</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6619647741317749</v>
+        <v>0.6614972949028015</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016187191009521</v>
+        <v>0.9016454815864563</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -929,282 +929,282 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>1244342</v>
+        <v>584658</v>
       </c>
       <c r="E4" t="n">
-        <v>11473760</v>
+        <v>2518880</v>
       </c>
       <c r="F4" t="n">
-        <v>360775</v>
+        <v>162268</v>
       </c>
       <c r="G4" t="n">
-        <v>9537</v>
+        <v>5067</v>
       </c>
       <c r="H4" t="n">
-        <v>19638</v>
+        <v>12735</v>
       </c>
       <c r="I4" t="n">
-        <v>1385</v>
+        <v>920</v>
       </c>
       <c r="J4" t="n">
-        <v>560</v>
+        <v>136</v>
       </c>
       <c r="K4" t="n">
-        <v>1315966</v>
+        <v>616299</v>
       </c>
       <c r="L4" t="n">
-        <v>1754224</v>
+        <v>782542</v>
       </c>
       <c r="M4" t="n">
-        <v>605461</v>
+        <v>263745</v>
       </c>
       <c r="N4" t="n">
-        <v>89527</v>
+        <v>36416</v>
       </c>
       <c r="O4" t="n">
-        <v>273876</v>
+        <v>128612</v>
       </c>
       <c r="P4" t="n">
-        <v>71138</v>
+        <v>32382</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999889731407166</v>
+        <v>0.9999892711639404</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9371960759162903</v>
+        <v>0.8850387930870056</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8712893128395081</v>
+        <v>0.7649244070053101</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8196137547492981</v>
+        <v>0.6806140542030334</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5995485186576843</v>
+        <v>0.3863481879234314</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8661754131317139</v>
+        <v>0.751730740070343</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9006498456001282</v>
+        <v>0.8100038170814514</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>820988</v>
+        <v>205971</v>
       </c>
       <c r="Z4" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AA4" t="n">
-        <v>332033</v>
+        <v>83251</v>
       </c>
       <c r="AB4" t="n">
-        <v>22018</v>
+        <v>5524</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>879281</v>
+        <v>220597</v>
       </c>
       <c r="AG4" t="n">
-        <v>1161969</v>
+        <v>290537</v>
       </c>
       <c r="AH4" t="n">
-        <v>529733</v>
+        <v>132714</v>
       </c>
       <c r="AI4" t="n">
-        <v>120475</v>
+        <v>30214</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199521</v>
+        <v>49934</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571588635444641</v>
+        <v>0.9570227861404419</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106193780899048</v>
+        <v>0.9106442928314209</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578745126724243</v>
+        <v>0.8577089309692383</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622039079666138</v>
+        <v>0.6616416573524475</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018170833587646</v>
+        <v>0.9018100500106812</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>44140</v>
+        <v>19850</v>
       </c>
       <c r="E5" t="n">
-        <v>481467</v>
+        <v>207082</v>
       </c>
       <c r="F5" t="n">
-        <v>3014158</v>
+        <v>618133</v>
       </c>
       <c r="G5" t="n">
-        <v>39521</v>
+        <v>15997</v>
       </c>
       <c r="H5" t="n">
-        <v>148151</v>
+        <v>68551</v>
       </c>
       <c r="I5" t="n">
-        <v>7988</v>
+        <v>4888</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1234716</v>
+        <v>553884</v>
       </c>
       <c r="L5" t="n">
-        <v>1635685</v>
+        <v>765656</v>
       </c>
       <c r="M5" t="n">
-        <v>721292</v>
+        <v>316387</v>
       </c>
       <c r="N5" t="n">
-        <v>165929</v>
+        <v>59256</v>
       </c>
       <c r="O5" t="n">
-        <v>271661</v>
+        <v>125251</v>
       </c>
       <c r="P5" t="n">
-        <v>81469</v>
+        <v>39698</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999914765357971</v>
+        <v>0.9999917149543762</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9611555337905884</v>
+        <v>0.9287168979644775</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9483749270439148</v>
+        <v>0.9056897163391113</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9797948002815247</v>
+        <v>0.9646605849266052</v>
       </c>
       <c r="U5" t="n">
-        <v>0.996109664440155</v>
+        <v>0.9941720366477966</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9916920065879822</v>
+        <v>0.9845356345176697</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9976759552955627</v>
+        <v>0.9956091642379761</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32176</v>
+        <v>8071</v>
       </c>
       <c r="Z5" t="n">
-        <v>340707</v>
+        <v>85325</v>
       </c>
       <c r="AA5" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AB5" t="n">
-        <v>39817</v>
+        <v>9981</v>
       </c>
       <c r="AC5" t="n">
-        <v>116549</v>
+        <v>29159</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>858074</v>
+        <v>214447</v>
       </c>
       <c r="AG5" t="n">
-        <v>1179891</v>
+        <v>295962</v>
       </c>
       <c r="AH5" t="n">
-        <v>531781</v>
+        <v>133169</v>
       </c>
       <c r="AI5" t="n">
-        <v>120733</v>
+        <v>30253</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200417</v>
+        <v>50120</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735417366027832</v>
+        <v>0.9734987616539001</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643356800079346</v>
+        <v>0.9642727375030518</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838341474533081</v>
+        <v>0.9838034510612488</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963266253471375</v>
+        <v>0.9963165521621704</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939092993736267</v>
+        <v>0.9939050674438477</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983839988708496</v>
+        <v>0.9983825087547302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>27361</v>
+        <v>11752</v>
       </c>
       <c r="E6" t="n">
-        <v>42373</v>
+        <v>17938</v>
       </c>
       <c r="F6" t="n">
-        <v>62952</v>
+        <v>17395</v>
       </c>
       <c r="G6" t="n">
-        <v>191232</v>
+        <v>30117</v>
       </c>
       <c r="H6" t="n">
-        <v>30548</v>
+        <v>10987</v>
       </c>
       <c r="I6" t="n">
-        <v>2605</v>
+        <v>1149</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25894</v>
+        <v>6499</v>
       </c>
       <c r="Z6" t="n">
-        <v>21451</v>
+        <v>5384</v>
       </c>
       <c r="AA6" t="n">
-        <v>43534</v>
+        <v>10901</v>
       </c>
       <c r="AB6" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AC6" t="n">
-        <v>27930</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>19099</v>
+        <v>12938</v>
       </c>
       <c r="F7" t="n">
-        <v>157299</v>
+        <v>73536</v>
       </c>
       <c r="G7" t="n">
-        <v>36101</v>
+        <v>13400</v>
       </c>
       <c r="H7" t="n">
-        <v>1765485</v>
+        <v>384334</v>
       </c>
       <c r="I7" t="n">
-        <v>58981</v>
+        <v>25336</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3246</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118564</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30328</v>
+        <v>7601</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>308</v>
+        <v>41</v>
       </c>
       <c r="D8" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>978</v>
+        <v>619</v>
       </c>
       <c r="F8" t="n">
-        <v>4043</v>
+        <v>2497</v>
       </c>
       <c r="G8" t="n">
-        <v>1567</v>
+        <v>774</v>
       </c>
       <c r="H8" t="n">
-        <v>74519</v>
+        <v>35747</v>
       </c>
       <c r="I8" t="n">
-        <v>691723</v>
+        <v>153648</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
